--- a/client/public/templates/customer_import_template_csp.xlsx
+++ b/client/public/templates/customer_import_template_csp.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\customer-CSP\client\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2BC3EF38-2499-44C3-83DD-06FF555715DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A45AA15-86E2-4F2B-8E19-DDC1A0C54BA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{BFC5101E-514D-4E77-BE0B-D61B0A445028}"/>
   </bookViews>
@@ -75,36 +75,6 @@
     <t>Remarks</t>
   </si>
   <si>
-    <r>
-      <t>Name</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Mobile No </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-  </si>
-  <si>
     <t>CIF01</t>
   </si>
   <si>
@@ -127,6 +97,12 @@
   </si>
   <si>
     <t>John Rose</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Mobile No</t>
   </si>
 </sst>
 </file>
@@ -142,8 +118,10 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <i/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -169,9 +147,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -507,8 +486,8 @@
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>13</v>
+      <c r="C1" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="D1" t="s">
         <v>2</v>
@@ -516,8 +495,8 @@
       <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" t="s">
-        <v>14</v>
+      <c r="F1" s="2" t="s">
+        <v>22</v>
       </c>
       <c r="G1" t="s">
         <v>4</v>
@@ -549,13 +528,13 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B2">
         <v>23423423478799</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D2" s="1">
         <v>37276</v>
@@ -567,7 +546,7 @@
         <v>9478787878</v>
       </c>
       <c r="G2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H2">
         <v>899899006644</v>
@@ -579,30 +558,30 @@
         <v>42356</v>
       </c>
       <c r="K2" t="s">
+        <v>16</v>
+      </c>
+      <c r="L2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M2" t="s">
         <v>18</v>
       </c>
-      <c r="L2" t="s">
+      <c r="N2" t="s">
+        <v>17</v>
+      </c>
+      <c r="O2" t="s">
         <v>19</v>
-      </c>
-      <c r="M2" t="s">
-        <v>20</v>
-      </c>
-      <c r="N2" t="s">
-        <v>19</v>
-      </c>
-      <c r="O2" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B3">
         <v>23423423471799</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D3" s="1">
         <v>37276</v>
@@ -614,7 +593,7 @@
         <v>9478787878</v>
       </c>
       <c r="G3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H3">
         <v>899899000644</v>
@@ -626,19 +605,19 @@
         <v>42356</v>
       </c>
       <c r="K3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N3" t="s">
         <v>18</v>
       </c>
-      <c r="L3" t="s">
+      <c r="O3" t="s">
         <v>19</v>
-      </c>
-      <c r="M3" t="s">
-        <v>19</v>
-      </c>
-      <c r="N3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O3" t="s">
-        <v>21</v>
       </c>
     </row>
   </sheetData>
